--- a/exports/colleges/7960_institute-of-hotel-management-ihm-bangalore.xlsx
+++ b/exports/colleges/7960_institute-of-hotel-management-ihm-bangalore.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHM</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.65 Lakhs</t>
+          <t>4.65 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 and NCHMCT JEE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NCHMCT JEE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>26 May - 20 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diploma in Hotel Management</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Diploma</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1 Year 6 Months</t>
+          <t>1 year 6 months</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10 + 2</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 May 2025</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MHM</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.99 Lakhs</t>
+          <t>2.99 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 June - 25 Jun 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UG Diploma in Vocational Courses</t>
+          <t>Craftsmanship Course</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Craftsmanship Course</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1 Year 6 Months</t>
+          <t>1 year 6 months</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10th passed</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 May 2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,17 +940,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BHM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B.Sc(HHA)</t>
+          <t>Bachelor of Science [B.Sc] (Hospitality and Hotel Administration)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B.Sc(HHA)</t>
+          <t>Bachelor of Science [B.Sc] (Hospitality and Hotel Administration)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 and NCHMCT JEE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NCHMCT JEE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Diploma in Hotel Management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Diploma</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Diploma</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Diploma</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>97,950</t>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 Year 6 Months</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 + 2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>MHM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M.Sc(HA)</t>
+          <t>Master of Science [M.Sc] (Hospitality Administration)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>M.Sc(HA)</t>
+          <t>Master of Science [M.Sc] (Hospitality Administration)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>UG Diploma in Vocational Courses</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Craftsmanship Course</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Craftsmanship Course</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34,850 - 87,050</t>
+          <t>34,850</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year 6 Months</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10th passed</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+          <t>B.Sc(HHA)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+          <t>B.Sc(HHA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diploma Food Production</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>M.Sc(HA)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Diploma Bakery And Confectionery</t>
+          <t>M.Sc(HA)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>97,950</t>
+          <t>2.99 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(HA) Hospitality Administration</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(HA) Hospitality Administration</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.99 Lakhs</t>
+          <t>34,850 - 87,050</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1436,51 +1436,299 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>B.Sc(HHA) Hospitality And Hotel Administration</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4.65 Lakhs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7960</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Diploma Food Production</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Diploma Food Production</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Diploma Food Production</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>97,950</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7960</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Diploma Bakery And Confectionery</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Diploma Bakery And Confectionery</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Diploma Bakery And Confectionery</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>97,950</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1 Year</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7960</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(HA) Hospitality Administration</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(HA) Hospitality Administration</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2.99 Lakhs</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7960</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Certification</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Certification (General)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>34,850 - 87,050</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
